--- a/output/HS_Code_Summary_Hitachi_Energy_129689.xlsx
+++ b/output/HS_Code_Summary_Hitachi_Energy_129689.xlsx
@@ -816,23 +816,23 @@
       </c>
       <c r="F15" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C15,'Export decl – položky'!$E$4:$E$25)</f>
-        <v/>
+        <v>2.09</v>
       </c>
       <c r="G15" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C15,'Export decl – položky'!$D$4:$D$25)</f>
-        <v/>
+        <v>3.18</v>
       </c>
       <c r="H15" s="7">
         <f>ROUND(G15/SUM($G$15:$G$31)*116.0,2)</f>
-        <v/>
+        <v>5.27</v>
       </c>
       <c r="I15" s="8">
         <f>SUMIF('Detail položek'!$F$4:$F$40,$C15,'Detail položek'!$G$4:$G$40)</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="J15" s="9">
         <f>ROUND(SUMIF('Detail položek'!$F$4:$F$40,$C15,'Detail položek'!$I$4:$I$40),2)</f>
-        <v/>
+        <v>664.0</v>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
@@ -888,23 +888,23 @@
       </c>
       <c r="F16" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C16,'Export decl – položky'!$E$4:$E$25)</f>
-        <v/>
+        <v>2.09</v>
       </c>
       <c r="G16" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C16,'Export decl – položky'!$D$4:$D$25)</f>
-        <v/>
+        <v>3.18</v>
       </c>
       <c r="H16" s="7">
         <f>ROUND(G16/SUM($G$15:$G$31)*116.0,2)</f>
-        <v/>
+        <v>5.27</v>
       </c>
       <c r="I16" s="8">
         <f>SUMIF('Detail položek'!$F$4:$F$40,$C16,'Detail položek'!$G$4:$G$40)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J16" s="9">
         <f>ROUND(SUMIF('Detail položek'!$F$4:$F$40,$C16,'Detail položek'!$I$4:$I$40),2)</f>
-        <v/>
+        <v>406.45</v>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
@@ -956,23 +956,23 @@
       </c>
       <c r="F17" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C17,'Export decl – položky'!$E$4:$E$25)</f>
-        <v/>
+        <v>2.09</v>
       </c>
       <c r="G17" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C17,'Export decl – položky'!$D$4:$D$25)</f>
-        <v/>
+        <v>3.18</v>
       </c>
       <c r="H17" s="7">
         <f>ROUND(G17/SUM($G$15:$G$31)*116.0,2)</f>
-        <v/>
+        <v>5.27</v>
       </c>
       <c r="I17" s="8">
         <f>SUMIF('Detail položek'!$F$4:$F$40,$C17,'Detail položek'!$G$4:$G$40)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="J17" s="9">
         <f>ROUND(SUMIF('Detail položek'!$F$4:$F$40,$C17,'Detail položek'!$I$4:$I$40),2)</f>
-        <v/>
+        <v>30215.35</v>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
@@ -1028,23 +1028,23 @@
       </c>
       <c r="F18" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C18,'Export decl – položky'!$E$4:$E$25)</f>
-        <v/>
+        <v>2.09</v>
       </c>
       <c r="G18" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C18,'Export decl – položky'!$D$4:$D$25)</f>
-        <v/>
+        <v>3.18</v>
       </c>
       <c r="H18" s="7">
         <f>ROUND(G18/SUM($G$15:$G$31)*116.0,2)</f>
-        <v/>
+        <v>5.27</v>
       </c>
       <c r="I18" s="8">
         <f>SUMIF('Detail položek'!$F$4:$F$40,$C18,'Detail položek'!$G$4:$G$40)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J18" s="9">
         <f>ROUND(SUMIF('Detail položek'!$F$4:$F$40,$C18,'Detail položek'!$I$4:$I$40),2)</f>
-        <v/>
+        <v>13.33</v>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
@@ -1096,23 +1096,23 @@
       </c>
       <c r="F19" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C19,'Export decl – položky'!$E$4:$E$25)</f>
-        <v/>
+        <v>2.09</v>
       </c>
       <c r="G19" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C19,'Export decl – položky'!$D$4:$D$25)</f>
-        <v/>
+        <v>3.18</v>
       </c>
       <c r="H19" s="7">
         <f>ROUND(G19/SUM($G$15:$G$31)*116.0,2)</f>
-        <v/>
+        <v>5.27</v>
       </c>
       <c r="I19" s="8">
         <f>SUMIF('Detail položek'!$F$4:$F$40,$C19,'Detail položek'!$G$4:$G$40)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J19" s="9">
         <f>ROUND(SUMIF('Detail položek'!$F$4:$F$40,$C19,'Detail položek'!$I$4:$I$40),2)</f>
-        <v/>
+        <v>8.33</v>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
@@ -1164,23 +1164,23 @@
       </c>
       <c r="F20" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C20,'Export decl – položky'!$E$4:$E$25)</f>
-        <v/>
+        <v>2.09</v>
       </c>
       <c r="G20" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C20,'Export decl – položky'!$D$4:$D$25)</f>
-        <v/>
+        <v>3.18</v>
       </c>
       <c r="H20" s="7">
         <f>ROUND(G20/SUM($G$15:$G$31)*116.0,2)</f>
-        <v/>
+        <v>5.27</v>
       </c>
       <c r="I20" s="8">
         <f>SUMIF('Detail položek'!$F$4:$F$40,$C20,'Detail položek'!$G$4:$G$40)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="J20" s="9">
         <f>ROUND(SUMIF('Detail položek'!$F$4:$F$40,$C20,'Detail položek'!$I$4:$I$40),2)</f>
-        <v/>
+        <v>756.0</v>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
@@ -1236,23 +1236,23 @@
       </c>
       <c r="F21" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C21,'Export decl – položky'!$E$4:$E$25)</f>
-        <v/>
+        <v>2.09</v>
       </c>
       <c r="G21" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C21,'Export decl – položky'!$D$4:$D$25)</f>
-        <v/>
+        <v>3.18</v>
       </c>
       <c r="H21" s="7">
         <f>ROUND(G21/SUM($G$15:$G$31)*116.0,2)</f>
-        <v/>
+        <v>5.27</v>
       </c>
       <c r="I21" s="8">
         <f>SUMIF('Detail položek'!$F$4:$F$40,$C21,'Detail položek'!$G$4:$G$40)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="J21" s="9">
         <f>ROUND(SUMIF('Detail položek'!$F$4:$F$40,$C21,'Detail položek'!$I$4:$I$40),2)</f>
-        <v/>
+        <v>2914.0</v>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
@@ -1308,23 +1308,23 @@
       </c>
       <c r="F22" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C22,'Export decl – položky'!$E$4:$E$25)</f>
-        <v/>
+        <v>6.27</v>
       </c>
       <c r="G22" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C22,'Export decl – položky'!$D$4:$D$25)</f>
-        <v/>
+        <v>9.54</v>
       </c>
       <c r="H22" s="7">
         <f>ROUND(G22/SUM($G$15:$G$31)*116.0,2)</f>
-        <v/>
+        <v>15.81</v>
       </c>
       <c r="I22" s="8">
         <f>SUMIF('Detail položek'!$F$4:$F$40,$C22,'Detail položek'!$G$4:$G$40)</f>
-        <v/>
+        <v>37</v>
       </c>
       <c r="J22" s="9">
         <f>ROUND(SUMIF('Detail položek'!$F$4:$F$40,$C22,'Detail položek'!$I$4:$I$40),2)</f>
-        <v/>
+        <v>12677.33</v>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
@@ -1380,23 +1380,23 @@
       </c>
       <c r="F23" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C23,'Export decl – položky'!$E$4:$E$25)</f>
-        <v/>
+        <v>2.09</v>
       </c>
       <c r="G23" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C23,'Export decl – položky'!$D$4:$D$25)</f>
-        <v/>
+        <v>3.18</v>
       </c>
       <c r="H23" s="7">
         <f>ROUND(G23/SUM($G$15:$G$31)*116.0,2)</f>
-        <v/>
+        <v>5.27</v>
       </c>
       <c r="I23" s="8">
         <f>SUMIF('Detail položek'!$F$4:$F$40,$C23,'Detail položek'!$G$4:$G$40)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J23" s="9">
         <f>ROUND(SUMIF('Detail položek'!$F$4:$F$40,$C23,'Detail položek'!$I$4:$I$40),2)</f>
-        <v/>
+        <v>630.0</v>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
@@ -1448,23 +1448,23 @@
       </c>
       <c r="F24" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C24,'Export decl – položky'!$E$4:$E$25)</f>
-        <v/>
+        <v>2.09</v>
       </c>
       <c r="G24" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C24,'Export decl – položky'!$D$4:$D$25)</f>
-        <v/>
+        <v>3.18</v>
       </c>
       <c r="H24" s="7">
         <f>ROUND(G24/SUM($G$15:$G$31)*116.0,2)</f>
-        <v/>
+        <v>5.27</v>
       </c>
       <c r="I24" s="8">
         <f>SUMIF('Detail položek'!$F$4:$F$40,$C24,'Detail položek'!$G$4:$G$40)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="J24" s="9">
         <f>ROUND(SUMIF('Detail položek'!$F$4:$F$40,$C24,'Detail položek'!$I$4:$I$40),2)</f>
-        <v/>
+        <v>255.3</v>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
@@ -1516,23 +1516,23 @@
       </c>
       <c r="F25" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C25,'Export decl – položky'!$E$4:$E$25)</f>
-        <v/>
+        <v>2.09</v>
       </c>
       <c r="G25" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C25,'Export decl – položky'!$D$4:$D$25)</f>
-        <v/>
+        <v>3.18</v>
       </c>
       <c r="H25" s="7">
         <f>ROUND(G25/SUM($G$15:$G$31)*116.0,2)</f>
-        <v/>
+        <v>5.27</v>
       </c>
       <c r="I25" s="8">
         <f>SUMIF('Detail položek'!$F$4:$F$40,$C25,'Detail položek'!$G$4:$G$40)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J25" s="9">
         <f>ROUND(SUMIF('Detail položek'!$F$4:$F$40,$C25,'Detail položek'!$I$4:$I$40),2)</f>
-        <v/>
+        <v>164.0</v>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
@@ -1584,23 +1584,23 @@
       </c>
       <c r="F26" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C26,'Export decl – položky'!$E$4:$E$25)</f>
-        <v/>
+        <v>2.09</v>
       </c>
       <c r="G26" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C26,'Export decl – položky'!$D$4:$D$25)</f>
-        <v/>
+        <v>3.18</v>
       </c>
       <c r="H26" s="7">
         <f>ROUND(G26/SUM($G$15:$G$31)*116.0,2)</f>
-        <v/>
+        <v>5.27</v>
       </c>
       <c r="I26" s="8">
         <f>SUMIF('Detail položek'!$F$4:$F$40,$C26,'Detail položek'!$G$4:$G$40)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="J26" s="9">
         <f>ROUND(SUMIF('Detail položek'!$F$4:$F$40,$C26,'Detail položek'!$I$4:$I$40),2)</f>
-        <v/>
+        <v>59.68</v>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
@@ -1652,23 +1652,23 @@
       </c>
       <c r="F27" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C27,'Export decl – položky'!$E$4:$E$25)</f>
-        <v/>
+        <v>2.11</v>
       </c>
       <c r="G27" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C27,'Export decl – položky'!$D$4:$D$25)</f>
-        <v/>
+        <v>3.22</v>
       </c>
       <c r="H27" s="7">
         <f>ROUND(G27/SUM($G$15:$G$31)*116.0,2)</f>
-        <v/>
+        <v>5.34</v>
       </c>
       <c r="I27" s="8">
         <f>SUMIF('Detail položek'!$F$4:$F$40,$C27,'Detail položek'!$G$4:$G$40)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="J27" s="9">
         <f>ROUND(SUMIF('Detail položek'!$F$4:$F$40,$C27,'Detail položek'!$I$4:$I$40),2)</f>
-        <v/>
+        <v>189.73</v>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
@@ -1724,23 +1724,23 @@
       </c>
       <c r="F28" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C28,'Export decl – položky'!$E$4:$E$25)</f>
-        <v/>
+        <v>4.18</v>
       </c>
       <c r="G28" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C28,'Export decl – položky'!$D$4:$D$25)</f>
-        <v/>
+        <v>6.36</v>
       </c>
       <c r="H28" s="7">
         <f>ROUND(G28/SUM($G$15:$G$31)*116.0,2)</f>
-        <v/>
+        <v>10.54</v>
       </c>
       <c r="I28" s="8">
         <f>SUMIF('Detail položek'!$F$4:$F$40,$C28,'Detail položek'!$G$4:$G$40)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="J28" s="9">
         <f>ROUND(SUMIF('Detail položek'!$F$4:$F$40,$C28,'Detail položek'!$I$4:$I$40),2)</f>
-        <v/>
+        <v>6396.5</v>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
@@ -1796,23 +1796,23 @@
       </c>
       <c r="F29" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C29,'Export decl – položky'!$E$4:$E$25)</f>
-        <v/>
+        <v>2.09</v>
       </c>
       <c r="G29" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C29,'Export decl – položky'!$D$4:$D$25)</f>
-        <v/>
+        <v>3.18</v>
       </c>
       <c r="H29" s="7">
         <f>ROUND(G29/SUM($G$15:$G$31)*116.0,2)</f>
-        <v/>
+        <v>5.27</v>
       </c>
       <c r="I29" s="8">
         <f>SUMIF('Detail položek'!$F$4:$F$40,$C29,'Detail položek'!$G$4:$G$40)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="J29" s="9">
         <f>ROUND(SUMIF('Detail položek'!$F$4:$F$40,$C29,'Detail položek'!$I$4:$I$40),2)</f>
-        <v/>
+        <v>25.0</v>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
@@ -1864,23 +1864,23 @@
       </c>
       <c r="F30" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C30,'Export decl – položky'!$E$4:$E$25)</f>
-        <v/>
+        <v>6.27</v>
       </c>
       <c r="G30" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C30,'Export decl – položky'!$D$4:$D$25)</f>
-        <v/>
+        <v>9.54</v>
       </c>
       <c r="H30" s="7">
         <f>ROUND(G30/SUM($G$15:$G$31)*116.0,2)</f>
-        <v/>
+        <v>15.81</v>
       </c>
       <c r="I30" s="8">
         <f>SUMIF('Detail položek'!$F$4:$F$40,$C30,'Detail položek'!$G$4:$G$40)</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="J30" s="9">
         <f>ROUND(SUMIF('Detail položek'!$F$4:$F$40,$C30,'Detail položek'!$I$4:$I$40),2)</f>
-        <v/>
+        <v>387.07</v>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
@@ -1936,23 +1936,23 @@
       </c>
       <c r="F31" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C31,'Export decl – položky'!$E$4:$E$25)</f>
-        <v/>
+        <v>2.09</v>
       </c>
       <c r="G31" s="7">
         <f>SUMIF('Export decl – položky'!$B$4:$B$25,$C31,'Export decl – položky'!$D$4:$D$25)</f>
-        <v/>
+        <v>3.18</v>
       </c>
       <c r="H31" s="7">
         <f>ROUND(G31/SUM($G$15:$G$31)*116.0,2)</f>
-        <v/>
+        <v>5.27</v>
       </c>
       <c r="I31" s="8">
         <f>SUMIF('Detail položek'!$F$4:$F$40,$C31,'Detail položek'!$G$4:$G$40)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="J31" s="9">
         <f>ROUND(SUMIF('Detail položek'!$F$4:$F$40,$C31,'Detail položek'!$I$4:$I$40),2)</f>
-        <v/>
+        <v>1199.94</v>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
@@ -1992,23 +1992,23 @@
       <c r="E32" s="12" t="n"/>
       <c r="F32" s="13">
         <f>SUM(F15:F31)</f>
-        <v/>
+        <v>46.0</v>
       </c>
       <c r="G32" s="13">
         <f>SUM(G15:G31)</f>
-        <v/>
+        <v>70.0</v>
       </c>
       <c r="H32" s="13">
         <f>SUM(H15:H31)</f>
-        <v/>
+        <v>116.01</v>
       </c>
       <c r="I32" s="14">
         <f>SUM(I15:I31)</f>
-        <v/>
+        <v>98</v>
       </c>
       <c r="J32" s="15">
         <f>SUM(J15:J31)</f>
-        <v/>
+        <v>56962.01</v>
       </c>
       <c r="K32" s="12" t="n"/>
       <c r="L32" s="12" t="n"/>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="G37" s="18">
         <f>G35-G36</f>
-        <v/>
+        <v>46.0</v>
       </c>
     </row>
     <row r="39">
@@ -2855,19 +2855,19 @@
       </c>
       <c r="C26" s="12">
         <f>SUM(C4:C25)</f>
-        <v/>
+        <v>98</v>
       </c>
       <c r="D26" s="13">
         <f>SUM(D4:D25)</f>
-        <v/>
+        <v>70.0</v>
       </c>
       <c r="E26" s="13">
         <f>SUM(E4:E25)</f>
-        <v/>
+        <v>46.0</v>
       </c>
       <c r="G26" s="15">
         <f>SUM(G4:G25)</f>
-        <v/>
+        <v>56962.01</v>
       </c>
     </row>
     <row r="28">
@@ -4483,11 +4483,11 @@
       </c>
       <c r="G41" s="12">
         <f>SUM(G4:G40)</f>
-        <v/>
+        <v>98</v>
       </c>
       <c r="I41" s="15">
         <f>SUM(I4:I40)</f>
-        <v/>
+        <v>56962.01</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
@@ -5145,11 +5145,11 @@
       </c>
       <c r="D29" s="12">
         <f>SUM(D7:D28)</f>
-        <v/>
+        <v>98</v>
       </c>
       <c r="E29" s="15">
         <f>SUM(E7:E28)</f>
-        <v/>
+        <v>56962.01</v>
       </c>
     </row>
     <row r="31">
@@ -5173,7 +5173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:B61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -5430,125 +5430,173 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="31" t="inlineStr">
-        <is>
-          <t>6) CELNÍ HODNOTA</t>
-        </is>
-      </c>
-      <c r="B39" s="32" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
+      <c r="A39" s="29" t="inlineStr">
+        <is>
+          <t>6) CELNÍ HODNOTA – ZÁKLAD PRO URČENÍ NUTNO POTVRDIT</t>
+        </is>
+      </c>
+      <c r="B39" s="30" t="inlineStr">
+        <is>
+          <t>K VYJASNĚNÍ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="22" t="inlineStr">
         <is>
+          <t>⚠ Faktura 129689 nese text: „THE VALUE OF THESE GOODS ARE LISTED FOR CUSTOMS PURPOSES ONLY“ a jde o převod mezi dvěma společnostmi skupiny Hitachi Energy (UK → CZ). Nejde tedy zřejmě o prodej. Pokud prodej neproběhl, nelze celní hodnotu určit převodní hodnotou (čl. 70 UCC) a je nutné použít některou z náhradních metod (čl. 74 UCC). Potvrďte s dovozcem, zda je zboží fakturováno a placeno, nebo jde o bezplatný převod.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>⚠ PŘEPRAVNÉ: Purchase Order 4502372958 ze dne 19.08.2026 je objednávka PŘEPRAVY u DSV Road Ltd – „2x pallets with small goods“ za 487,10 GBP (Terms of Delivery DAP Stone, měna GBP). Nejde o fakturu za zboží.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>➤ Nutno vyjasnit, zda je těchto 487,10 GBP již obsaženo v částce 56 962,01 GBP. Při dodací podmínce CPT Trutnov má přepravu hradit prodávající, a je-li fakturována zvlášť, je nutné náklady až po místo vstupu do EU k celní hodnotě PŘIČÍST (čl. 71 UCC); náklady po vstupu do EU se naopak odečítají, jsou-li vykázány odděleně.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="45" customHeight="1">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>⚠ NESROVNALOST: pokyn k odbavení uvádí „TUZ úsek: 22 000,- CZK“ (tuzemský úsek), což je zhruba 780 GBP – tedy VÍCE než celkové přepravné 487,10 GBP podle PO 4502372958 za celou trasu. Tyto dva údaje si odporují; před výpočtem celní hodnoty je nutné je sjednotit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="22" t="inlineStr"/>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
           <t>Fakturovaná hodnota: 56 962,01 GBP. Dodací podmínka CPT Trutnov, Česká republika – přeprava až do místa určení je součástí ceny.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="45" customHeight="1">
-      <c r="A41" s="22" t="inlineStr">
+    <row r="46" ht="45" customHeight="1">
+      <c r="A46" s="22" t="inlineStr">
         <is>
           <t>V pokynu k odbavení je uvedeno: „TUZ úsek: 22 000,- CZK“ (tuzemský úsek přepravy). Náklady na přepravu po vstupu zboží na celní území EU lze z celní hodnoty odečíst, jsou-li vykázány odděleně – rozdělení a uplatnění je na vás, do souhrnu jsem je nezapočítal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="22" t="inlineStr">
-        <is>
-          <t>Obchodní sleva: v dokladech není uvedena žádná sleva, proporcionální rozpuštění slevy se tedy neprovádělo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="22" t="inlineStr">
-        <is>
-          <t>Kurz pro přepočet GBP → CZK stanovte podle celního kurzu platného ke dni přijetí celního prohlášení.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="31" t="inlineStr">
-        <is>
-          <t>7) PROVOZNÍ POZNÁMKY K ZÁSILCE</t>
-        </is>
-      </c>
-      <c r="B45" s="32" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="22" t="inlineStr">
-        <is>
-          <t>Přeprava: DSV Road s.r.o. (Alena Miková), zásilka GBPFT608004151 / MSA850/012. Vývozní MRN (SCP): 26GB000246SZVJOHJ0.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="22" t="inlineStr">
         <is>
+          <t>Obchodní sleva: v dokladech není uvedena žádná sleva, proporcionální rozpuštění slevy se tedy neprovádělo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>Kurz pro přepočet GBP → CZK stanovte podle celního kurzu platného ke dni přijetí celního prohlášení.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="31" t="inlineStr">
+        <is>
+          <t>7) PROVOZNÍ POZNÁMKY K ZÁSILCE</t>
+        </is>
+      </c>
+      <c r="B50" s="32" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>Přeprava: DSV Road s.r.o. (Alena Miková), zásilka GBPFT608004151 / MSA850/012. Vývozní MRN (SCP): 26GB000246SZVJOHJ0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
           <t>Pan Jahnholz uvádí, že jde o přepravu BEZ T1, a žádá o potvrzení – ověřte, zda k zásilce existuje tranzitní doklad, nebo zda se clí přímo na základě vývozního MRN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="22" t="inlineStr">
-        <is>
-          <t>DSV k zásilce neměla dovozní fakturu (měla pouze objednávku a export declaration sheet); fakturu 129689 dodala přímo Hitachi Energy (Mathias Jahnholz) – ta je podkladem tohoto souhrnu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="22" t="inlineStr">
-        <is>
-          <t>Vykládka: 14./15.09.2026, Trutnov, Průmyslová 137. Kontakt příjemce: Monika Lutterová, +420 704 844 676.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="22" t="inlineStr">
-        <is>
-          <t>Vývozní kontrola: Supplier's Declaration concerning Export Control potvrzuje u VŠECH položek Dual-Use = No, vojenské zboží N/A, ITAR N/A – zboží nepodléhá vývozním omezením.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="29" t="inlineStr">
-        <is>
-          <t>8) POZNÁMKA K POPISŮM V ČEŠTINĚ</t>
-        </is>
-      </c>
-      <c r="B52" s="30" t="inlineStr">
-        <is>
-          <t>POZOR</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="22" t="inlineStr">
         <is>
+          <t>DSV k zásilce neměla dovozní fakturu (měla pouze objednávku a export declaration sheet); fakturu 129689 dodala přímo Hitachi Energy (Mathias Jahnholz) – ta je podkladem tohoto souhrnu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>Vykládka: 14./15.09.2026, Trutnov, Průmyslová 137. Kontakt příjemce: Monika Lutterová, +420 704 844 676.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>Vývozní kontrola: Supplier's Declaration concerning Export Control potvrzuje u VŠECH položek Dual-Use = No, vojenské zboží N/A, ITAR N/A – zboží nepodléhá vývozním omezením.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="45" customHeight="1">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>PO 4502372958 (19.08.2026) = objednávka přepravy u DSV Road Ltd, 487,10 GBP, dodání 28.08.2026. Obsahuje rovněž prohlášení dodavatele, že zboží NENÍ ruského původu a neobsahuje železné ani ocelové výrobky ruského původu – využitelné k doložení souladu se sankčním režimem (čl. 3g nařízení 833/2014).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>„Dispozice IMPORT“ je nevyplněný formulář objednávky celních služeb Maurice Ward. Požaduje přesně tyto údaje: český popis zboží, TARIC, hodnotu, nákladové kusy, hrubou a čistou hmotnost – všechny jsou na listu „Souhrn HS“. Formulář je dosud nevyplněný a nepodepsaný; před odbavením jej nechte dovozce doplnit a podepsat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="29" t="inlineStr">
+        <is>
+          <t>8) POZNÁMKA K POPISŮM V ČEŠTINĚ</t>
+        </is>
+      </c>
+      <c r="B59" s="30" t="inlineStr">
+        <is>
+          <t>POZOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
           <t>Zdrojové doklady (faktura, packing note, export declaration, supplier's declaration) jsou POUZE v angličtině – český popis zboží v nich není k dispozici.</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="45" customHeight="1">
-      <c r="A54" s="22" t="inlineStr">
+    <row r="61" ht="45" customHeight="1">
+      <c r="A61" s="22" t="inlineStr">
         <is>
           <t>Sloupec „Popis zboží (CZ)“ na listu „Souhrn HS“ je proto překlad podle znění kombinované nomenklatury k danému HS kódu, nikoli převzatý údaj ze zdrojového dokladu. Původní anglický popis je zachován ve vedlejším sloupci.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="44">
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A45:B45"/>
     <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A61:B61"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="A7:B7"/>
@@ -5557,9 +5605,11 @@
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A50:B50"/>
     <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A57:B57"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A5:B5"/>
@@ -5575,10 +5625,12 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A52:B52"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A34:B34"/>
   </mergeCells>

--- a/output/HS_Code_Summary_Hitachi_Energy_129689.xlsx
+++ b/output/HS_Code_Summary_Hitachi_Energy_129689.xlsx
@@ -141,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -199,6 +199,9 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5173,7 +5176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -5503,135 +5506,415 @@
     <row r="50">
       <c r="A50" s="31" t="inlineStr">
         <is>
+          <t>6a) DOPRAVNÉ – CO O NĚM VÍME Z DOKLADŮ</t>
+        </is>
+      </c>
+      <c r="B50" s="32" t="inlineStr">
+        <is>
+          <t>PŘEHLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>Přehled všech údajů o dopravném, které se v doložených dokladech vyskytují:</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="33" t="inlineStr">
+        <is>
+          <t>Dopravce</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>DSV Road Ltd, Scandinavia House, Refinery Road, Parkeston, Harwich CO12 4QG, GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   – identifikace</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>EORI GB759894254003, VAT GB7598942540 (v export declaration veden jako Forwarding Agent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   – kontakt v CZ</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>DSV Road s.r.o., Alena Miková, Prologis Park Rudná, K Vypichu 731, Nučice 252 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="33" t="inlineStr">
+        <is>
+          <t>Objednávka přepravy</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>Purchase Order 4502372958 ze dne 19.08.2026 (Hitachi Energy UK Ltd → DSV Road Ltd)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   – reference</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>Q-8384061; dodavatel č. 1000174058; rámcová smlouva 129689 HWUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   – předmět</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>„2x pallets with small goods“, 1 položka, dodání 28.08.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="33" t="inlineStr">
+        <is>
+          <t>DOPRAVNÉ dle PO</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>487,10 GBP  (Net Price 487,10 / Net Value 487,10 / Total net value excl. tax 487,10 GBP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   – dodací podmínka PO</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>DAP Stone (tj. podmínka objednávky přepravy, nikoli zásilky)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="33" t="inlineStr">
+        <is>
+          <t>„TUZ úsek“ dle pokynu</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>22 000,- CZK – uvedeno v e-mailu pana Jahnholze jako tuzemský (český) úsek přepravy</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="33" t="inlineStr">
+        <is>
+          <t>Incoterm zásilky</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>CPT Trutnov, Česká republika (shodně na faktuře i v export declaration)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="33" t="inlineStr">
+        <is>
+          <t>Přeprava – způsob</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>silniční (Road). Packing Note uvádí „Despatch Method: DB SCHENKER“ – DB Schenker je součástí DSV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="33" t="inlineStr">
+        <is>
+          <t>Transportation Ref. No.</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>40257145950465208908 (export declaration, pole 16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="33" t="inlineStr">
+        <is>
+          <t>Zásilka / STT</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>GBPFT608004151, MSA850/012; vývozní MRN 26GB000246SZVJOHJ0</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="33" t="inlineStr">
+        <is>
+          <t>Místo výstupu z GB</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>NEUVEDENO („Výstup: unknown“)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="33" t="inlineStr">
+        <is>
+          <t>Místo vstupu do EU</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>NEUVEDENO („Vstup do EU: unknown“) – bez něj nelze rozdělit dopravné na část před a po vstupu do EU</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="33" t="inlineStr">
+        <is>
+          <t>SPZ vozidla</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>NEUVEDENO („SPZ: unknown“)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="25" t="inlineStr">
+        <is>
+          <t>6b) DOPRAVNÉ A CELNÍ HODNOTA – CO JE TŘEBA VYŘEŠIT</t>
+        </is>
+      </c>
+      <c r="B70" s="26" t="inlineStr">
+        <is>
+          <t>NEVYŘEŠENO</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="45" customHeight="1">
+      <c r="A71" s="22" t="inlineStr">
+        <is>
+          <t>❗ ZJIŠTĚNÍ: částka 56 962,01 GBP na faktuře 129689 je PŘESNĚ součtem 37 řádků zboží. Faktura neobsahuje žádný řádek za dopravné, balné ani pojištění. Dopravné tedy ve fakturované částce prokazatelně NENÍ zahrnuto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="22" t="inlineStr">
+        <is>
+          <t>❗ To je v rozporu s dodací podmínkou CPT Trutnov, podle níž přepravu do místa určení hradí prodávající a měla by být v ceně. Buď je podmínka uvedena nesprávně, nebo se dopravné fakturuje mimo tuto fakturu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" s="22" t="inlineStr">
+        <is>
+          <t>➤ DŮSLEDEK PRO CELNÍ HODNOTU: náklady na dopravu až do místa vstupu zboží na celní území EU se do celní hodnoty PŘIČÍTAJÍ (čl. 71 odst. 1 písm. e) UCC). Náklady na dopravu po vstupu do EU se naopak nezahrnují, jsou-li vykázány odděleně (čl. 72 písm. a) UCC). Dopravné je proto nutné rozdělit na úsek před vstupem do EU a po něm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="22" t="inlineStr">
+        <is>
+          <t>➤ PROBLÉM: místo vstupu do EU není v pokynu uvedeno („unknown“), takže rozdělení zatím nelze provést. Vyžádejte si trasu (přes který přístav / hraniční přechod zásilka vstoupila do EU).</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" s="22" t="inlineStr">
+        <is>
+          <t>⚠ NESROVNALOST ČÁSTEK: 22 000 CZK za samotný tuzemský úsek je při jakémkoli reálném kurzu (cca 26–30 CZK/GBP) zhruba 730–850 GBP, tedy VÍCE než celé dopravné 487,10 GBP podle PO 4502372958 za celou trasu Stone → Trutnov. Část nemůže být větší než celek – jeden z těchto údajů je chybný nebo se každý týká něčeho jiného (např. 22 000 CZK může zahrnovat i celní služby, skladné či dodání koncovému příjemci).</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="45" customHeight="1">
+      <c r="A76" s="22" t="inlineStr">
+        <is>
+          <t>➤ K DOTAZU NA DOVOZCE / DSV: (1) je 487,10 GBP dopravné za celou trasu Stone → Trutnov? (2) co přesně zahrnuje 22 000 CZK a jakého úseku se týká? (3) jaké je místo vstupu do EU? (4) má být dopravné přičteno k celní hodnotě, nebo je již v ceně zboží?</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="22" t="inlineStr">
+        <is>
+          <t>Pozn.: PO 4502372958 je objednávka Hitachi Energy UK u DSV – není to faktura dopravce. Pro doložení celní hodnoty celnímu úřadu bude nejspíš potřeba faktura DSV za přepravu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="31" t="inlineStr">
+        <is>
           <t>7) PROVOZNÍ POZNÁMKY K ZÁSILCE</t>
         </is>
       </c>
-      <c r="B50" s="32" t="inlineStr">
+      <c r="B79" s="32" t="inlineStr">
         <is>
           <t>INFO</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="22" t="inlineStr">
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="22" t="inlineStr">
         <is>
           <t>Přeprava: DSV Road s.r.o. (Alena Miková), zásilka GBPFT608004151 / MSA850/012. Vývozní MRN (SCP): 26GB000246SZVJOHJ0.</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="22" t="inlineStr">
+    <row r="81" ht="30" customHeight="1">
+      <c r="A81" s="22" t="inlineStr">
         <is>
           <t>Pan Jahnholz uvádí, že jde o přepravu BEZ T1, a žádá o potvrzení – ověřte, zda k zásilce existuje tranzitní doklad, nebo zda se clí přímo na základě vývozního MRN.</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="22" t="inlineStr">
+    <row r="82" ht="30" customHeight="1">
+      <c r="A82" s="22" t="inlineStr">
         <is>
           <t>DSV k zásilce neměla dovozní fakturu (měla pouze objednávku a export declaration sheet); fakturu 129689 dodala přímo Hitachi Energy (Mathias Jahnholz) – ta je podkladem tohoto souhrnu.</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="22" t="inlineStr">
+    <row r="83" ht="15" customHeight="1">
+      <c r="A83" s="22" t="inlineStr">
         <is>
           <t>Vykládka: 14./15.09.2026, Trutnov, Průmyslová 137. Kontakt příjemce: Monika Lutterová, +420 704 844 676.</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="22" t="inlineStr">
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="22" t="inlineStr">
         <is>
           <t>Vývozní kontrola: Supplier's Declaration concerning Export Control potvrzuje u VŠECH položek Dual-Use = No, vojenské zboží N/A, ITAR N/A – zboží nepodléhá vývozním omezením.</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="45" customHeight="1">
-      <c r="A56" s="22" t="inlineStr">
+    <row r="85" ht="45" customHeight="1">
+      <c r="A85" s="22" t="inlineStr">
         <is>
           <t>PO 4502372958 (19.08.2026) = objednávka přepravy u DSV Road Ltd, 487,10 GBP, dodání 28.08.2026. Obsahuje rovněž prohlášení dodavatele, že zboží NENÍ ruského původu a neobsahuje železné ani ocelové výrobky ruského původu – využitelné k doložení souladu se sankčním režimem (čl. 3g nařízení 833/2014).</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" s="22" t="inlineStr">
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" s="22" t="inlineStr">
         <is>
           <t>„Dispozice IMPORT“ je nevyplněný formulář objednávky celních služeb Maurice Ward. Požaduje přesně tyto údaje: český popis zboží, TARIC, hodnotu, nákladové kusy, hrubou a čistou hmotnost – všechny jsou na listu „Souhrn HS“. Formulář je dosud nevyplněný a nepodepsaný; před odbavením jej nechte dovozce doplnit a podepsat.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="29" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="29" t="inlineStr">
         <is>
           <t>8) POZNÁMKA K POPISŮM V ČEŠTINĚ</t>
         </is>
       </c>
-      <c r="B59" s="30" t="inlineStr">
+      <c r="B88" s="30" t="inlineStr">
         <is>
           <t>POZOR</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="22" t="inlineStr">
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="22" t="inlineStr">
         <is>
           <t>Zdrojové doklady (faktura, packing note, export declaration, supplier's declaration) jsou POUZE v angličtině – český popis zboží v nich není k dispozici.</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="45" customHeight="1">
-      <c r="A61" s="22" t="inlineStr">
+    <row r="90" ht="45" customHeight="1">
+      <c r="A90" s="22" t="inlineStr">
         <is>
           <t>Sloupec „Popis zboží (CZ)“ na listu „Souhrn HS“ je proto překlad podle znění kombinované nomenklatury k danému HS kódu, nikoli převzatý údaj ze zdrojového dokladu. Původní anglický popis je zachován ve vedlejším sloupci.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="52">
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A73:B73"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A61:B61"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A54:B54"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A90:B90"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A80:B80"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A76:B76"/>
     <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A71:B71"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A42:B42"/>
     <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A85:B85"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A53:B53"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A72:B72"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A52:B52"/>
     <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A81:B81"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A83:B83"/>
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A77:B77"/>
     <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/HS_Code_Summary_Hitachi_Energy_129689.xlsx
+++ b/output/HS_Code_Summary_Hitachi_Energy_129689.xlsx
@@ -5176,7 +5176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B90"/>
+  <dimension ref="A1:B100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -5776,95 +5776,164 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="31" t="inlineStr">
-        <is>
-          <t>7) PROVOZNÍ POZNÁMKY K ZÁSILCE</t>
-        </is>
-      </c>
-      <c r="B79" s="32" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="30" customHeight="1">
+      <c r="A79" s="25" t="inlineStr">
+        <is>
+          <t>7) TRANZIT / T1 – NEMÁME, STAV NEPOTVRZEN</t>
+        </is>
+      </c>
+      <c r="B79" s="26" t="inlineStr">
+        <is>
+          <t>NEVYŘEŠENO</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="45" customHeight="1">
       <c r="A80" s="22" t="inlineStr">
         <is>
-          <t>Přeprava: DSV Road s.r.o. (Alena Miková), zásilka GBPFT608004151 / MSA850/012. Vývozní MRN (SCP): 26GB000246SZVJOHJ0.</t>
+          <t>❌ Mezi doloženými doklady NENÍ žádné tranzitní celní prohlášení (T1) ani jiný tranzitní doklad. K dispozici máme pouze: Customs Invoice 129689, Packing Note, Export Declaration Instruction Sheet 1400045712, Supplier's Declaration (export control), PO 4502372958 a nevyplněný formulář Dispozice IMPORT.</t>
         </is>
       </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="22" t="inlineStr">
         <is>
-          <t>Pan Jahnholz uvádí, že jde o přepravu BEZ T1, a žádá o potvrzení – ověřte, zda k zásilce existuje tranzitní doklad, nebo zda se clí přímo na základě vývozního MRN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="30" customHeight="1">
+          <t xml:space="preserve">V celé e-mailové korespondenci se T1 zmiňuje jedinkrát – pan Jahnholz (Hitachi Energy) 11.09.2026: „Pokud vím, jedná se o přepravu bez T1; prosím o potvrzení.“ </t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="45" customHeight="1">
       <c r="A82" s="22" t="inlineStr">
         <is>
+          <t>⚠ TOTO POTVRZENÍ NIKDY NEPŘIŠLO. DSV (paní Miková) na dotaz k T1 neodpověděla; její poslední zpráva zní „já více dokladů k dispozici nemám“. Stav tranzitu je tedy otevřený – nelze vycházet z toho, že T1 neexistuje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="30" customHeight="1">
+      <c r="A83" s="22" t="inlineStr">
+        <is>
+          <t>Jediné MRN v korespondenci je 26GB000246SZVJOHJ0, které DSV označuje jako „SCP MRN“. Z označení nelze určit, zda jde o britské vývozní celní prohlášení, nebo o tranzitní prohlášení.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="45" customHeight="1">
+      <c r="A84" s="22" t="inlineStr">
+        <is>
+          <t>⚠ POZOR: Spojené království je smluvní stranou Úmluvy o společném tranzitním režimu, takže i T1 otevřené v GB nese MRN s předponou GB. Prefix „26GB…“ tedy sám o sobě NEDOKAZUJE, že jde o vývozní a nikoli tranzitní doklad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" s="22" t="inlineStr">
+        <is>
+          <t>➤ PROČ NA TOM ZÁLEŽÍ: pokud T1 existuje, musí je Maurice Ward u celního úřadu určení řádně a včas ukončit a JSD musí na tento předchozí doklad odkazovat. Pokud T1 neexistuje, muselo být zboží propuštěno do celního režimu již v místě vstupu do EU – a to místo je dosud „unknown“. Ani jedna varianta zatím není doložena.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="22" t="inlineStr">
+        <is>
+          <t>➤ Formulář Dispozice IMPORT má kolonku „Tranzitní celní prohlášení (T1): ANO / NE“ i „Celní úřad určení“ NEVYPLNĚNÉ, včetně závazku „V případě tohoto režimu se zavazujeme T1 včas a řádně ukončit“.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="45" customHeight="1">
+      <c r="A87" s="22" t="inlineStr">
+        <is>
+          <t>➤ DOTAZ NA DSV (paní Miková) – vyžádat písemně: (1) bylo k zásilce otevřeno tranzitní prohlášení T1, ano či ne? (2) pokud ano, jaké je MRN tranzitu a který je celní úřad určení? (3) co přesně je MRN 26GB000246SZVJOHJ0 – vývozní, nebo tranzitní prohlášení? (4) kde zásilka vstoupila na celní území EU?</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="31" t="inlineStr">
+        <is>
+          <t>8) PROVOZNÍ POZNÁMKY K ZÁSILCE</t>
+        </is>
+      </c>
+      <c r="B89" s="32" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="22" t="inlineStr">
+        <is>
+          <t>Přeprava: DSV Road s.r.o. (Alena Miková), zásilka GBPFT608004151 / MSA850/012. Vývozní MRN (SCP): 26GB000246SZVJOHJ0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" s="22" t="inlineStr">
+        <is>
+          <t>Tranzit / T1: viz samostatná sekce 7 – stav není potvrzen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="22" t="inlineStr">
+        <is>
           <t>DSV k zásilce neměla dovozní fakturu (měla pouze objednávku a export declaration sheet); fakturu 129689 dodala přímo Hitachi Energy (Mathias Jahnholz) – ta je podkladem tohoto souhrnu.</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="15" customHeight="1">
-      <c r="A83" s="22" t="inlineStr">
+    <row r="93" ht="15" customHeight="1">
+      <c r="A93" s="22" t="inlineStr">
         <is>
           <t>Vykládka: 14./15.09.2026, Trutnov, Průmyslová 137. Kontakt příjemce: Monika Lutterová, +420 704 844 676.</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="30" customHeight="1">
-      <c r="A84" s="22" t="inlineStr">
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="22" t="inlineStr">
         <is>
           <t>Vývozní kontrola: Supplier's Declaration concerning Export Control potvrzuje u VŠECH položek Dual-Use = No, vojenské zboží N/A, ITAR N/A – zboží nepodléhá vývozním omezením.</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="45" customHeight="1">
-      <c r="A85" s="22" t="inlineStr">
+    <row r="95" ht="45" customHeight="1">
+      <c r="A95" s="22" t="inlineStr">
         <is>
           <t>PO 4502372958 (19.08.2026) = objednávka přepravy u DSV Road Ltd, 487,10 GBP, dodání 28.08.2026. Obsahuje rovněž prohlášení dodavatele, že zboží NENÍ ruského původu a neobsahuje železné ani ocelové výrobky ruského původu – využitelné k doložení souladu se sankčním režimem (čl. 3g nařízení 833/2014).</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" s="22" t="inlineStr">
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" s="22" t="inlineStr">
         <is>
           <t>„Dispozice IMPORT“ je nevyplněný formulář objednávky celních služeb Maurice Ward. Požaduje přesně tyto údaje: český popis zboží, TARIC, hodnotu, nákladové kusy, hrubou a čistou hmotnost – všechny jsou na listu „Souhrn HS“. Formulář je dosud nevyplněný a nepodepsaný; před odbavením jej nechte dovozce doplnit a podepsat.</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="29" t="inlineStr">
-        <is>
-          <t>8) POZNÁMKA K POPISŮM V ČEŠTINĚ</t>
-        </is>
-      </c>
-      <c r="B88" s="30" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="29" t="inlineStr">
+        <is>
+          <t>9) POZNÁMKA K POPISŮM V ČEŠTINĚ</t>
+        </is>
+      </c>
+      <c r="B98" s="30" t="inlineStr">
         <is>
           <t>POZOR</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="22" t="inlineStr">
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="22" t="inlineStr">
         <is>
           <t>Zdrojové doklady (faktura, packing note, export declaration, supplier's declaration) jsou POUZE v angličtině – český popis zboží v nich není k dispozici.</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="45" customHeight="1">
-      <c r="A90" s="22" t="inlineStr">
+    <row r="100" ht="45" customHeight="1">
+      <c r="A100" s="22" t="inlineStr">
         <is>
           <t>Sloupec „Popis zboží (CZ)“ na listu „Souhrn HS“ je proto překlad podle znění kombinované nomenklatury k danému HS kódu, nikoli převzatý údaj ze zdrojového dokladu. Původní anglický popis je zachován ve vedlejším sloupci.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="60">
     <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A92:B92"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A82:B82"/>
     <mergeCell ref="A73:B73"/>
@@ -5872,15 +5941,17 @@
     <mergeCell ref="A51:B51"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A94:B94"/>
     <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A87:B87"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A99:B99"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="A75:B75"/>
     <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A89:B89"/>
     <mergeCell ref="A74:B74"/>
     <mergeCell ref="A80:B80"/>
     <mergeCell ref="A18:B18"/>
@@ -5888,6 +5959,7 @@
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A95:B95"/>
     <mergeCell ref="A76:B76"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A71:B71"/>
@@ -5901,15 +5973,19 @@
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A91:B91"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A100:B100"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A96:B96"/>
     <mergeCell ref="A72:B72"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A93:B93"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A83:B83"/>
     <mergeCell ref="A44:B44"/>
